--- a/data/trans_camb/P19C09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C09-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,25</t>
+          <t>-3,53; -0,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,57</t>
+          <t>-2,64; 1,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -0,15</t>
+          <t>-3,68; -0,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,74</t>
+          <t>-3,47; 0,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,58</t>
+          <t>-3,18; -0,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,37</t>
+          <t>-2,6; 0,39</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,19; 0,54</t>
+          <t>-76,02; -0,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,8; 63,28</t>
+          <t>-56,86; 50,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,19; -2,69</t>
+          <t>-61,41; -0,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 17,33</t>
+          <t>-57,98; 14,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,21; -15,37</t>
+          <t>-61,67; -15,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 10,31</t>
+          <t>-51,93; 10,32</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,18</t>
+          <t>-2,46; -0,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,72</t>
+          <t>-0,84; 1,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,01</t>
+          <t>-0,39; 1,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,06</t>
+          <t>-0,96; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,57</t>
+          <t>-1,03; 0,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,01</t>
+          <t>-0,48; 1,1</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,06; -5,88</t>
+          <t>-72,48; -3,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 92,76</t>
+          <t>-26,59; 94,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 152,54</t>
+          <t>-19,17; 146,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 82,67</t>
+          <t>-39,38; 88,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 36,14</t>
+          <t>-38,78; 36,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 59,35</t>
+          <t>-19,1; 65,79</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,32</t>
+          <t>-0,45; 3,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,03</t>
+          <t>-0,78; 3,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,41</t>
+          <t>-3,02; 2,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,22</t>
+          <t>-2,11; 3,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,52</t>
+          <t>-1,09; 2,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,63</t>
+          <t>-0,91; 2,55</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 508,92</t>
+          <t>-31,41; 453,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 433,59</t>
+          <t>-41,36; 436,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 115,16</t>
+          <t>-61,08; 99,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 142,31</t>
+          <t>-42,54; 140,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 151,88</t>
+          <t>-32,98; 134,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 151,29</t>
+          <t>-27,41; 154,48</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; -0,13</t>
+          <t>-1,74; -0,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,22</t>
+          <t>-0,69; 1,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,59</t>
+          <t>-1,16; 0,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,46</t>
+          <t>-1,39; 0,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,07</t>
+          <t>-1,19; -0,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,56</t>
+          <t>-0,76; 0,5</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,57; -4,64</t>
+          <t>-55,57; -2,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 57,11</t>
+          <t>-23,04; 59,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 22,13</t>
+          <t>-32,5; 22,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 17,74</t>
+          <t>-37,88; 19,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 3,22</t>
+          <t>-37,53; -1,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 21,86</t>
+          <t>-23,77; 19,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C09-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,19</t>
+          <t>-3,58; -0,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,28</t>
+          <t>-2,53; 1,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,18</t>
+          <t>-3,9; -0,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,52</t>
+          <t>-3,32; 0,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; -0,65</t>
+          <t>-3,21; -0,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,39</t>
+          <t>-2,58; 0,42</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,02; -0,6</t>
+          <t>-76,05; 5,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 50,26</t>
+          <t>-56,16; 53,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,41; -0,18</t>
+          <t>-61,35; -5,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,98; 14,17</t>
+          <t>-57,51; 18,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,67; -15,38</t>
+          <t>-62,0; -19,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 10,32</t>
+          <t>-52,15; 12,14</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,19</t>
+          <t>-2,41; -0,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,7</t>
+          <t>-0,84; 1,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,95</t>
+          <t>-0,3; 1,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,09</t>
+          <t>-0,85; 1,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,6</t>
+          <t>-0,95; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,1</t>
+          <t>-0,47; 1,08</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,48; -3,92</t>
+          <t>-72,32; -2,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 94,34</t>
+          <t>-25,93; 98,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 146,35</t>
+          <t>-13,76; 164,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 88,16</t>
+          <t>-37,54; 105,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 36,17</t>
+          <t>-38,52; 38,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 65,79</t>
+          <t>-17,79; 64,52</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,89</t>
+          <t>-0,39; 4,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,07</t>
+          <t>-0,83; 3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,25</t>
+          <t>-3,2; 2,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,22</t>
+          <t>-1,89; 3,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,35</t>
+          <t>-0,95; 2,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,55</t>
+          <t>-0,6; 2,59</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 453,88</t>
+          <t>-32,54; 538,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 436,14</t>
+          <t>-43,33; 389,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,08; 99,48</t>
+          <t>-64,69; 109,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 140,5</t>
+          <t>-39,14; 153,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 134,62</t>
+          <t>-30,9; 155,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 154,48</t>
+          <t>-21,1; 135,85</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; -0,06</t>
+          <t>-1,75; -0,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,25</t>
+          <t>-0,65; 1,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,61</t>
+          <t>-1,24; 0,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,55</t>
+          <t>-1,41; 0,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,04</t>
+          <t>-1,23; 0,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,5</t>
+          <t>-0,77; 0,58</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,57; -2,29</t>
+          <t>-55,55; -2,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 59,22</t>
+          <t>-22,04; 57,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 22,81</t>
+          <t>-34,39; 23,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 19,83</t>
+          <t>-38,94; 17,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,53; -1,31</t>
+          <t>-37,66; 1,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 19,83</t>
+          <t>-24,35; 23,13</t>
         </is>
       </c>
     </row>
